--- a/data/trans_orig/IQ18D_M-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IQ18D_M-Habitat-trans_orig.xlsx
@@ -526,7 +526,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Tiempo medio que tuvieron que esperar hasta ser atendidos por el médico en minutos</t>
+          <t>Tiempo medio que tuvieron que esperar hasta ser atendidos por el médico en minutos (tasa de respuesta: 91,62%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,62 +716,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>19,77; 23,73</t>
+          <t>19,79; 23,76</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>17,61; 22,69</t>
+          <t>17,39; 23,04</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>15,19; 21,88</t>
+          <t>15,1; 21,92</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>10,31; 23,82</t>
+          <t>9,83; 22,63</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>19,82; 23,51</t>
+          <t>19,73; 23,45</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>17,5; 23,1</t>
+          <t>17,59; 22,78</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>12,69; 16,98</t>
+          <t>12,67; 16,85</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>7,67; 28,15</t>
+          <t>7,71; 29,25</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>20,34; 23,06</t>
+          <t>20,4; 22,9</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>18,16; 21,65</t>
+          <t>18,19; 22,0</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>14,26; 18,18</t>
+          <t>14,33; 18,21</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>9,79; 22,64</t>
+          <t>9,81; 22,81</t>
         </is>
       </c>
     </row>
@@ -856,62 +856,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>21,86; 28,8</t>
+          <t>22,04; 28,57</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>18,95; 22,86</t>
+          <t>19,03; 22,83</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>17,12; 22,18</t>
+          <t>17,15; 22,38</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>14,03; 38,25</t>
+          <t>14,02; 40,58</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>18,62; 22,66</t>
+          <t>18,58; 22,43</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>19,23; 23,1</t>
+          <t>19,57; 23,55</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>17,15; 21,58</t>
+          <t>17,12; 21,69</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>10,48; 15,73</t>
+          <t>10,52; 15,65</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>20,74; 24,53</t>
+          <t>20,62; 24,39</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>19,78; 22,45</t>
+          <t>19,63; 22,46</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>17,55; 20,93</t>
+          <t>17,5; 20,93</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>12,54; 22,67</t>
+          <t>12,62; 22,87</t>
         </is>
       </c>
     </row>
@@ -996,62 +996,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>18,52; 22,93</t>
+          <t>18,59; 23,14</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>18,28; 24,02</t>
+          <t>18,15; 24,0</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>13,35; 17,05</t>
+          <t>13,24; 17,01</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>11,16; 22,22</t>
+          <t>11,33; 22,3</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>18,63; 23,81</t>
+          <t>18,84; 24,03</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>18,0; 22,31</t>
+          <t>18,06; 22,28</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>15,22; 23,65</t>
+          <t>15,31; 23,17</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>15,84; 33,12</t>
+          <t>15,12; 29,85</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>19,17; 22,76</t>
+          <t>19,17; 22,63</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>18,72; 22,33</t>
+          <t>18,8; 22,3</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>14,72; 19,36</t>
+          <t>14,8; 19,24</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>15,06; 25,29</t>
+          <t>15,03; 25,64</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1136,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>18,21; 22,08</t>
+          <t>18,26; 22,05</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>17,68; 21,35</t>
+          <t>17,62; 21,43</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>14,8; 17,88</t>
+          <t>14,8; 17,94</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>12,05; 24,02</t>
+          <t>11,51; 23,36</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>19,86; 24,85</t>
+          <t>19,79; 24,81</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>18,03; 22,74</t>
+          <t>18,16; 22,43</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>14,91; 18,29</t>
+          <t>14,74; 18,09</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>13,19; 54,98</t>
+          <t>13,15; 52,71</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>19,71; 22,64</t>
+          <t>19,6; 22,55</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>18,28; 21,19</t>
+          <t>18,28; 21,24</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>15,27; 17,43</t>
+          <t>15,09; 17,46</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>14,2; 35,06</t>
+          <t>14,05; 33,06</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1276,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>20,59; 23,11</t>
+          <t>20,53; 23,06</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>19,05; 21,31</t>
+          <t>18,99; 21,2</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>15,98; 18,19</t>
+          <t>16,1; 18,37</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>14,09; 21,95</t>
+          <t>14,05; 22,45</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>20,12; 22,51</t>
+          <t>20,16; 22,36</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>19,27; 21,55</t>
+          <t>19,26; 21,75</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>15,97; 18,61</t>
+          <t>16,07; 18,57</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>13,77; 22,99</t>
+          <t>13,64; 23,75</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>20,73; 22,36</t>
+          <t>20,71; 22,3</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>19,47; 21,01</t>
+          <t>19,45; 21,05</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>16,32; 17,97</t>
+          <t>16,26; 17,96</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>14,68; 20,61</t>
+          <t>14,53; 20,56</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IQ18D_M-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IQ18D_M-Habitat-trans_orig.xlsx
@@ -716,62 +716,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>19,79; 23,76</t>
+          <t>19,81; 23,87</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>17,39; 23,04</t>
+          <t>17,43; 22,88</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>15,1; 21,92</t>
+          <t>14,95; 22,09</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>9,83; 22,63</t>
+          <t>10,14; 23,51</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>19,73; 23,45</t>
+          <t>19,66; 23,27</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>17,59; 22,78</t>
+          <t>17,55; 22,71</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>12,67; 16,85</t>
+          <t>12,77; 16,8</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>7,71; 29,25</t>
+          <t>7,69; 29,77</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>20,4; 22,9</t>
+          <t>20,23; 22,86</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>18,19; 22,0</t>
+          <t>18,08; 21,79</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>14,33; 18,21</t>
+          <t>14,29; 18,04</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>9,81; 22,81</t>
+          <t>9,99; 22,71</t>
         </is>
       </c>
     </row>
@@ -856,62 +856,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>22,04; 28,57</t>
+          <t>22,16; 29,25</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>19,03; 22,83</t>
+          <t>18,96; 22,68</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>17,15; 22,38</t>
+          <t>17,05; 22,27</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>14,02; 40,58</t>
+          <t>13,99; 35,88</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>18,58; 22,43</t>
+          <t>18,4; 22,37</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>19,57; 23,55</t>
+          <t>19,5; 23,43</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>17,12; 21,69</t>
+          <t>17,21; 21,65</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>10,52; 15,65</t>
+          <t>10,32; 15,84</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>20,62; 24,39</t>
+          <t>20,75; 24,43</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>19,63; 22,46</t>
+          <t>19,71; 22,6</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>17,5; 20,93</t>
+          <t>17,51; 20,87</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>12,62; 22,87</t>
+          <t>12,41; 21,14</t>
         </is>
       </c>
     </row>
@@ -996,62 +996,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>18,59; 23,14</t>
+          <t>18,55; 23,04</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>18,15; 24,0</t>
+          <t>18,24; 24,15</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>13,24; 17,01</t>
+          <t>13,3; 17,01</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>11,33; 22,3</t>
+          <t>11,56; 23,24</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>18,84; 24,03</t>
+          <t>18,65; 23,57</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>18,06; 22,28</t>
+          <t>17,98; 22,4</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>15,31; 23,17</t>
+          <t>15,32; 23,73</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>15,12; 29,85</t>
+          <t>15,59; 30,09</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>19,17; 22,63</t>
+          <t>19,15; 22,52</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>18,8; 22,3</t>
+          <t>18,73; 22,35</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>14,8; 19,24</t>
+          <t>14,78; 19,16</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>15,03; 25,64</t>
+          <t>14,99; 25,02</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1136,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>18,26; 22,05</t>
+          <t>18,36; 22,03</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>17,62; 21,43</t>
+          <t>17,67; 21,4</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>14,8; 17,94</t>
+          <t>14,91; 17,91</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>11,51; 23,36</t>
+          <t>12,11; 23,9</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>19,79; 24,81</t>
+          <t>19,9; 24,81</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>18,16; 22,43</t>
+          <t>17,93; 22,79</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>14,74; 18,09</t>
+          <t>14,63; 17,96</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>13,15; 52,71</t>
+          <t>12,73; 54,57</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>19,6; 22,55</t>
+          <t>19,75; 22,77</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>18,28; 21,24</t>
+          <t>18,34; 21,31</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>15,09; 17,46</t>
+          <t>15,22; 17,49</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>14,05; 33,06</t>
+          <t>14,36; 33,69</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1276,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>20,53; 23,06</t>
+          <t>20,58; 23,14</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>18,99; 21,2</t>
+          <t>19,01; 21,25</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>16,1; 18,37</t>
+          <t>16,06; 18,27</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>14,05; 22,45</t>
+          <t>14,3; 22,63</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>20,16; 22,36</t>
+          <t>20,18; 22,44</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>19,26; 21,75</t>
+          <t>19,24; 21,49</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>16,07; 18,57</t>
+          <t>16,01; 18,51</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>13,64; 23,75</t>
+          <t>13,63; 22,59</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>20,71; 22,3</t>
+          <t>20,67; 22,35</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>19,45; 21,05</t>
+          <t>19,47; 21,02</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>16,26; 17,96</t>
+          <t>16,31; 17,96</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>14,53; 20,56</t>
+          <t>14,55; 20,73</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IQ18D_M-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IQ18D_M-Habitat-trans_orig.xlsx
@@ -526,13 +526,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Tiempo medio que tuvieron que esperar hasta ser atendidos por el médico en minutos (tasa de respuesta: 91,62%)</t>
+          <t>Tiempo medio en minutos que tuvieron que esperar desde que llegaron hasta ser atendidos/as en la última consulta médica (tasa de respuesta: 91,62%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -540,7 +540,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -648,42 +648,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>21,54</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>19,86</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>14,51</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>13,09</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>21,64</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>19,75</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>17,4</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>14,98</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>21,54</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>19,86</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>14,51</t>
-        </is>
-      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>12,98</t>
+          <t>15,06</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -703,7 +703,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>13,86</t>
+          <t>14,0</t>
         </is>
       </c>
     </row>
@@ -716,62 +716,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>19,81; 23,87</t>
+          <t>19,82; 23,51</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>17,43; 22,88</t>
+          <t>17,5; 23,1</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>14,95; 22,09</t>
+          <t>12,69; 16,98</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>10,14; 23,51</t>
+          <t>7,65; 28,74</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>19,66; 23,27</t>
+          <t>19,77; 23,73</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>17,55; 22,71</t>
+          <t>17,61; 22,69</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>12,77; 16,8</t>
+          <t>15,19; 21,88</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>7,69; 29,77</t>
+          <t>10,29; 24,6</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>20,23; 22,86</t>
+          <t>20,34; 23,06</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>18,08; 21,79</t>
+          <t>18,16; 21,65</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>14,29; 18,04</t>
+          <t>14,26; 18,18</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>9,99; 22,71</t>
+          <t>9,88; 22,58</t>
         </is>
       </c>
     </row>
@@ -788,42 +788,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>20,21</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>21,3</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>18,98</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>12,29</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>24,59</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>20,65</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>19,01</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>19,77</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>20,21</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>21,3</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>18,98</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>12,41</t>
+          <t>18,12</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -843,7 +843,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>15,16</t>
+          <t>14,5</t>
         </is>
       </c>
     </row>
@@ -856,62 +856,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>22,16; 29,25</t>
+          <t>18,62; 22,66</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>18,96; 22,68</t>
+          <t>19,23; 23,1</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>17,05; 22,27</t>
+          <t>17,15; 21,58</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>13,99; 35,88</t>
+          <t>10,32; 15,32</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>18,4; 22,37</t>
+          <t>21,86; 28,8</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>19,5; 23,43</t>
+          <t>18,95; 22,86</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>17,21; 21,65</t>
+          <t>17,12; 22,18</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>10,32; 15,84</t>
+          <t>12,9; 34,95</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>20,75; 24,43</t>
+          <t>20,74; 24,53</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>19,71; 22,6</t>
+          <t>19,78; 22,45</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>17,51; 20,87</t>
+          <t>17,55; 20,93</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>12,41; 21,14</t>
+          <t>12,14; 21,4</t>
         </is>
       </c>
     </row>
@@ -928,42 +928,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>20,85</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>19,95</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>17,83</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>21,21</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>20,56</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>20,74</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>14,93</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>16,08</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>20,85</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>19,95</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>17,83</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>21,2</t>
+          <t>17,13</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>18,82</t>
+          <t>19,36</t>
         </is>
       </c>
     </row>
@@ -996,62 +996,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>18,55; 23,04</t>
+          <t>18,63; 23,81</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>18,24; 24,15</t>
+          <t>18,0; 22,31</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>13,3; 17,01</t>
+          <t>15,22; 23,65</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>11,56; 23,24</t>
+          <t>15,89; 34,72</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>18,65; 23,57</t>
+          <t>18,52; 22,93</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>17,98; 22,4</t>
+          <t>18,28; 24,02</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>15,32; 23,73</t>
+          <t>13,35; 17,05</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>15,59; 30,09</t>
+          <t>12,58; 23,42</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>19,15; 22,52</t>
+          <t>19,17; 22,76</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>18,73; 22,35</t>
+          <t>18,72; 22,33</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>14,78; 19,16</t>
+          <t>14,72; 19,36</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>14,99; 25,02</t>
+          <t>15,74; 26,57</t>
         </is>
       </c>
     </row>
@@ -1068,62 +1068,62 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>22,16</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>19,99</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>16,23</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>24,25</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>19,94</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>19,4</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>16,23</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>16,17</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>22,16</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>19,99</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>15,59</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>21,04</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>19,7</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
         <is>
           <t>16,23</t>
         </is>
       </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>23,84</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>21,04</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>19,7</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>16,23</t>
-        </is>
-      </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>19,89</t>
+          <t>19,64</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1136,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>18,36; 22,03</t>
+          <t>19,86; 24,85</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>17,67; 21,4</t>
+          <t>18,03; 22,74</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>14,91; 17,91</t>
+          <t>14,91; 18,29</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>12,11; 23,9</t>
+          <t>13,19; 56,27</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>19,9; 24,81</t>
+          <t>18,21; 22,08</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>17,93; 22,79</t>
+          <t>17,68; 21,35</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>14,63; 17,96</t>
+          <t>14,8; 17,88</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>12,73; 54,57</t>
+          <t>11,62; 22,76</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>19,75; 22,77</t>
+          <t>19,71; 22,64</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>18,34; 21,31</t>
+          <t>18,28; 21,19</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>15,22; 17,49</t>
+          <t>15,27; 17,43</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>14,36; 33,69</t>
+          <t>14,06; 35,37</t>
         </is>
       </c>
     </row>
@@ -1208,42 +1208,42 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>21,2</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>20,34</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>17,11</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>17,07</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
           <t>21,68</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>20,1</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>17,02</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>16,99</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>21,2</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>20,34</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>17,11</t>
-        </is>
-      </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>16,97</t>
+          <t>16,59</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1263,7 +1263,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>16,98</t>
+          <t>16,86</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1276,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>20,58; 23,14</t>
+          <t>20,12; 22,51</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>19,01; 21,25</t>
+          <t>19,27; 21,55</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>16,06; 18,27</t>
+          <t>15,97; 18,61</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>14,3; 22,63</t>
+          <t>13,8; 23,49</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>20,18; 22,44</t>
+          <t>20,59; 23,11</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>19,24; 21,49</t>
+          <t>19,05; 21,31</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>16,01; 18,51</t>
+          <t>15,98; 18,19</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>13,63; 22,59</t>
+          <t>13,84; 20,95</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>20,67; 22,35</t>
+          <t>20,73; 22,36</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>19,47; 21,02</t>
+          <t>19,47; 21,01</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>16,31; 17,96</t>
+          <t>16,32; 17,97</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>14,55; 20,73</t>
+          <t>14,58; 20,29</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IQ18D_M-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IQ18D_M-Habitat-trans_orig.xlsx
@@ -16,7 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +127,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +140,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +509,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N14"/>
+  <dimension ref="A1:N19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -646,419 +651,271 @@
           <t>Media</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>21,54</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>19,86</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>14,51</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>13,09</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>21,64</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>19,75</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>17,4</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>15,06</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>21,59</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>19,81</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>15,88</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>14,0</t>
-        </is>
+      <c r="C4" s="5" t="n">
+        <v>21.54217682365847</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>19.86411404467644</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>14.50547211467534</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>13.09436924544622</v>
+      </c>
+      <c r="G4" s="5" t="n">
+        <v>21.64206973798302</v>
+      </c>
+      <c r="H4" s="5" t="n">
+        <v>19.75489291958325</v>
+      </c>
+      <c r="I4" s="5" t="n">
+        <v>17.4009228570026</v>
+      </c>
+      <c r="J4" s="5" t="n">
+        <v>15.06253401763505</v>
+      </c>
+      <c r="K4" s="5" t="n">
+        <v>21.58894767302002</v>
+      </c>
+      <c r="L4" s="5" t="n">
+        <v>19.81214835142992</v>
+      </c>
+      <c r="M4" s="5" t="n">
+        <v>15.88374695886237</v>
+      </c>
+      <c r="N4" s="5" t="n">
+        <v>14.00173453376045</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>19,82; 23,51</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>17,5; 23,1</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>12,69; 16,98</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>7,65; 28,74</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>19,77; 23,73</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>17,61; 22,69</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>15,19; 21,88</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>10,29; 24,6</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>20,34; 23,06</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>18,16; 21,65</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>14,26; 18,18</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>9,88; 22,58</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>19.8190365634213</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>17.49790857831918</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>12.6920185045277</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>7.648235711038529</v>
+      </c>
+      <c r="G5" s="5" t="n">
+        <v>19.7741074358513</v>
+      </c>
+      <c r="H5" s="5" t="n">
+        <v>17.61389960563075</v>
+      </c>
+      <c r="I5" s="5" t="n">
+        <v>15.19450870386075</v>
+      </c>
+      <c r="J5" s="5" t="n">
+        <v>10.29111851896938</v>
+      </c>
+      <c r="K5" s="5" t="n">
+        <v>20.3365972906821</v>
+      </c>
+      <c r="L5" s="5" t="n">
+        <v>18.16074035708038</v>
+      </c>
+      <c r="M5" s="5" t="n">
+        <v>14.26494837612001</v>
+      </c>
+      <c r="N5" s="5" t="n">
+        <v>9.880704227319656</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>23.50502056405014</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>23.09690224195583</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>16.98133528719585</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>28.7352589587582</v>
+      </c>
+      <c r="G6" s="5" t="n">
+        <v>23.72673339169918</v>
+      </c>
+      <c r="H6" s="5" t="n">
+        <v>22.68794125330711</v>
+      </c>
+      <c r="I6" s="5" t="n">
+        <v>21.88159100751081</v>
+      </c>
+      <c r="J6" s="5" t="n">
+        <v>24.60082018619119</v>
+      </c>
+      <c r="K6" s="5" t="n">
+        <v>23.06374376882157</v>
+      </c>
+      <c r="L6" s="5" t="n">
+        <v>21.65013944866392</v>
+      </c>
+      <c r="M6" s="5" t="n">
+        <v>18.17779687137788</v>
+      </c>
+      <c r="N6" s="5" t="n">
+        <v>22.57932462444546</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>10-50.000 hab</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Media</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>20,21</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>21,3</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>18,98</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>12,29</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>24,59</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>20,65</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>19,01</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>18,12</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>22,33</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>20,99</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>18,99</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>14,5</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>18,62; 22,66</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>19,23; 23,1</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>17,15; 21,58</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>10,32; 15,32</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>21,86; 28,8</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>18,95; 22,86</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>17,12; 22,18</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>12,9; 34,95</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>20,74; 24,53</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>19,78; 22,45</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>17,55; 20,93</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>12,14; 21,4</t>
-        </is>
+      <c r="C7" s="5" t="n">
+        <v>20.21246977922366</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>21.30046075631286</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>18.97788935547316</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>12.28721943657947</v>
+      </c>
+      <c r="G7" s="5" t="n">
+        <v>24.58526222080723</v>
+      </c>
+      <c r="H7" s="5" t="n">
+        <v>20.64901377486361</v>
+      </c>
+      <c r="I7" s="5" t="n">
+        <v>19.00632141288301</v>
+      </c>
+      <c r="J7" s="5" t="n">
+        <v>18.12173258944617</v>
+      </c>
+      <c r="K7" s="5" t="n">
+        <v>22.325930247873</v>
+      </c>
+      <c r="L7" s="5" t="n">
+        <v>20.98556045805782</v>
+      </c>
+      <c r="M7" s="5" t="n">
+        <v>18.99161435865121</v>
+      </c>
+      <c r="N7" s="5" t="n">
+        <v>14.49724193058415</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>&gt;50.000 hab</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Media</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>20,85</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>19,95</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>17,83</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>21,21</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>20,56</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>20,74</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>14,93</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>17,13</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>20,71</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>20,33</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>16,4</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>19,36</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>18.61649363186827</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>19.22752675492987</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>17.15287035263098</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>10.31837078710851</v>
+      </c>
+      <c r="G8" s="5" t="n">
+        <v>21.85879925696125</v>
+      </c>
+      <c r="H8" s="5" t="n">
+        <v>18.95091462006543</v>
+      </c>
+      <c r="I8" s="5" t="n">
+        <v>17.12279583792959</v>
+      </c>
+      <c r="J8" s="5" t="n">
+        <v>12.9022130617418</v>
+      </c>
+      <c r="K8" s="5" t="n">
+        <v>20.7384014231466</v>
+      </c>
+      <c r="L8" s="5" t="n">
+        <v>19.78265191507767</v>
+      </c>
+      <c r="M8" s="5" t="n">
+        <v>17.55240079982412</v>
+      </c>
+      <c r="N8" s="5" t="n">
+        <v>12.14053730789234</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>18,63; 23,81</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>18,0; 22,31</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>15,22; 23,65</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>15,89; 34,72</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>18,52; 22,93</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>18,28; 24,02</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>13,35; 17,05</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>12,58; 23,42</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>19,17; 22,76</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>18,72; 22,33</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>14,72; 19,36</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>15,74; 26,57</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>22.6594542339741</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>23.09649459023846</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>21.57816233485847</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>15.32199050198682</v>
+      </c>
+      <c r="G9" s="5" t="n">
+        <v>28.79645427569651</v>
+      </c>
+      <c r="H9" s="5" t="n">
+        <v>22.85776293906827</v>
+      </c>
+      <c r="I9" s="5" t="n">
+        <v>22.18035897079617</v>
+      </c>
+      <c r="J9" s="5" t="n">
+        <v>34.95125853245722</v>
+      </c>
+      <c r="K9" s="5" t="n">
+        <v>24.53124610020877</v>
+      </c>
+      <c r="L9" s="5" t="n">
+        <v>22.45354122676228</v>
+      </c>
+      <c r="M9" s="5" t="n">
+        <v>20.92644485548615</v>
+      </c>
+      <c r="N9" s="5" t="n">
+        <v>21.39782541959013</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Capitales</t>
+          <t>&gt;50.000 hab</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -1066,277 +923,405 @@
           <t>Media</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>22,16</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>19,99</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>16,23</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>24,25</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>19,94</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>19,4</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>16,23</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>15,59</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>21,04</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>19,7</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>16,23</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>19,64</t>
-        </is>
+      <c r="C10" s="5" t="n">
+        <v>20.84759163067558</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>19.94751665723859</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>17.8343016716727</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>21.21092934951915</v>
+      </c>
+      <c r="G10" s="5" t="n">
+        <v>20.56167159605328</v>
+      </c>
+      <c r="H10" s="5" t="n">
+        <v>20.74145559023727</v>
+      </c>
+      <c r="I10" s="5" t="n">
+        <v>14.93030245017093</v>
+      </c>
+      <c r="J10" s="5" t="n">
+        <v>17.12617317922737</v>
+      </c>
+      <c r="K10" s="5" t="n">
+        <v>20.70985192608608</v>
+      </c>
+      <c r="L10" s="5" t="n">
+        <v>20.32931164377072</v>
+      </c>
+      <c r="M10" s="5" t="n">
+        <v>16.40089728633972</v>
+      </c>
+      <c r="N10" s="5" t="n">
+        <v>19.35911333742733</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>19,86; 24,85</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>18,03; 22,74</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>14,91; 18,29</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>13,19; 56,27</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>18,21; 22,08</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>17,68; 21,35</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>14,8; 17,88</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>11,62; 22,76</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>19,71; 22,64</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>18,28; 21,19</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>15,27; 17,43</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>14,06; 35,37</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>18.62506544809635</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>17.99745863407092</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>15.21661877170934</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>15.89442324303191</v>
+      </c>
+      <c r="G11" s="5" t="n">
+        <v>18.51567087994063</v>
+      </c>
+      <c r="H11" s="5" t="n">
+        <v>18.2794371438106</v>
+      </c>
+      <c r="I11" s="5" t="n">
+        <v>13.34797709857377</v>
+      </c>
+      <c r="J11" s="5" t="n">
+        <v>12.58411222347634</v>
+      </c>
+      <c r="K11" s="5" t="n">
+        <v>19.16724945138731</v>
+      </c>
+      <c r="L11" s="5" t="n">
+        <v>18.72317508828696</v>
+      </c>
+      <c r="M11" s="5" t="n">
+        <v>14.72455881900457</v>
+      </c>
+      <c r="N11" s="5" t="n">
+        <v>15.74228466353566</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>23.80980112787502</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>22.31324478521906</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>23.65226070446662</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>34.72239797336011</v>
+      </c>
+      <c r="G12" s="5" t="n">
+        <v>22.93105324853653</v>
+      </c>
+      <c r="H12" s="5" t="n">
+        <v>24.01549928192133</v>
+      </c>
+      <c r="I12" s="5" t="n">
+        <v>17.04980179569651</v>
+      </c>
+      <c r="J12" s="5" t="n">
+        <v>23.41946964794861</v>
+      </c>
+      <c r="K12" s="5" t="n">
+        <v>22.7595637095021</v>
+      </c>
+      <c r="L12" s="5" t="n">
+        <v>22.32538068539961</v>
+      </c>
+      <c r="M12" s="5" t="n">
+        <v>19.35718944690407</v>
+      </c>
+      <c r="N12" s="5" t="n">
+        <v>26.56770765226445</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Capitales</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>22.16434911282274</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>19.99286724602921</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>16.23005985077451</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>24.24526325558762</v>
+      </c>
+      <c r="G13" s="5" t="n">
+        <v>19.94423029052621</v>
+      </c>
+      <c r="H13" s="5" t="n">
+        <v>19.40408970018662</v>
+      </c>
+      <c r="I13" s="5" t="n">
+        <v>16.22596073199727</v>
+      </c>
+      <c r="J13" s="5" t="n">
+        <v>15.59278244374461</v>
+      </c>
+      <c r="K13" s="5" t="n">
+        <v>21.03688737483015</v>
+      </c>
+      <c r="L13" s="5" t="n">
+        <v>19.69932108050016</v>
+      </c>
+      <c r="M13" s="5" t="n">
+        <v>16.22795140484771</v>
+      </c>
+      <c r="N13" s="5" t="n">
+        <v>19.64353818386894</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>19.86176516351768</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>18.03055041853087</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>14.90963710429286</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>13.19086749089611</v>
+      </c>
+      <c r="G14" s="5" t="n">
+        <v>18.20730290134122</v>
+      </c>
+      <c r="H14" s="5" t="n">
+        <v>17.68036273031074</v>
+      </c>
+      <c r="I14" s="5" t="n">
+        <v>14.80367167050903</v>
+      </c>
+      <c r="J14" s="5" t="n">
+        <v>11.62271440088096</v>
+      </c>
+      <c r="K14" s="5" t="n">
+        <v>19.70932885687423</v>
+      </c>
+      <c r="L14" s="5" t="n">
+        <v>18.28204337677123</v>
+      </c>
+      <c r="M14" s="5" t="n">
+        <v>15.26769230207399</v>
+      </c>
+      <c r="N14" s="5" t="n">
+        <v>14.06167463136751</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>24.85280559107019</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>22.74094907233448</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>18.2881647653626</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>56.26783625138139</v>
+      </c>
+      <c r="G15" s="5" t="n">
+        <v>22.08022170886105</v>
+      </c>
+      <c r="H15" s="5" t="n">
+        <v>21.35467463027735</v>
+      </c>
+      <c r="I15" s="5" t="n">
+        <v>17.88181745497993</v>
+      </c>
+      <c r="J15" s="5" t="n">
+        <v>22.7625029514567</v>
+      </c>
+      <c r="K15" s="5" t="n">
+        <v>22.63745379677227</v>
+      </c>
+      <c r="L15" s="5" t="n">
+        <v>21.18973027926936</v>
+      </c>
+      <c r="M15" s="5" t="n">
+        <v>17.42905845370314</v>
+      </c>
+      <c r="N15" s="5" t="n">
+        <v>35.37388073099589</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>Media</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>21,2</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>20,34</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>17,11</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>17,07</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>21,68</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>20,1</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>17,02</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>16,59</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>21,44</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>20,22</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>17,07</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>16,86</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>20,12; 22,51</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>19,27; 21,55</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>15,97; 18,61</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>13,8; 23,49</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>20,59; 23,11</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>19,05; 21,31</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>15,98; 18,19</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>13,84; 20,95</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>20,73; 22,36</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>19,47; 21,01</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>16,32; 17,97</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>14,58; 20,29</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="C16" s="5" t="n">
+        <v>21.20315367394295</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>20.34115060108572</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>17.10992561735796</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>17.07415936286198</v>
+      </c>
+      <c r="G16" s="5" t="n">
+        <v>21.68045002578471</v>
+      </c>
+      <c r="H16" s="5" t="n">
+        <v>20.10049855844353</v>
+      </c>
+      <c r="I16" s="5" t="n">
+        <v>17.02227172167003</v>
+      </c>
+      <c r="J16" s="5" t="n">
+        <v>16.58984697811489</v>
+      </c>
+      <c r="K16" s="5" t="n">
+        <v>21.43586351863019</v>
+      </c>
+      <c r="L16" s="5" t="n">
+        <v>20.22420121244805</v>
+      </c>
+      <c r="M16" s="5" t="n">
+        <v>17.06674495947114</v>
+      </c>
+      <c r="N16" s="5" t="n">
+        <v>16.856725395439</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>20.12439648941209</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>19.27295014365711</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>15.96789560650419</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>13.80329169288218</v>
+      </c>
+      <c r="G17" s="5" t="n">
+        <v>20.58500862176672</v>
+      </c>
+      <c r="H17" s="5" t="n">
+        <v>19.05194290084968</v>
+      </c>
+      <c r="I17" s="5" t="n">
+        <v>15.97721124196729</v>
+      </c>
+      <c r="J17" s="5" t="n">
+        <v>13.84105478791669</v>
+      </c>
+      <c r="K17" s="5" t="n">
+        <v>20.73365726329215</v>
+      </c>
+      <c r="L17" s="5" t="n">
+        <v>19.47063881498873</v>
+      </c>
+      <c r="M17" s="5" t="n">
+        <v>16.31656524892515</v>
+      </c>
+      <c r="N17" s="5" t="n">
+        <v>14.58252901200152</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>22.51042969387167</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>21.54544377606527</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>18.61264151134981</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>23.49436494382347</v>
+      </c>
+      <c r="G18" s="5" t="n">
+        <v>23.11160996594476</v>
+      </c>
+      <c r="H18" s="5" t="n">
+        <v>21.31238342408531</v>
+      </c>
+      <c r="I18" s="5" t="n">
+        <v>18.18597390600504</v>
+      </c>
+      <c r="J18" s="5" t="n">
+        <v>20.95348885620419</v>
+      </c>
+      <c r="K18" s="5" t="n">
+        <v>22.36101052858173</v>
+      </c>
+      <c r="L18" s="5" t="n">
+        <v>21.01251229446648</v>
+      </c>
+      <c r="M18" s="5" t="n">
+        <v>17.9723657073723</v>
+      </c>
+      <c r="N18" s="5" t="n">
+        <v>20.2898407291083</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -1344,15 +1329,15 @@
     </row>
   </sheetData>
   <mergeCells count="9">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
     <mergeCell ref="A1:B2"/>
     <mergeCell ref="C1:F1"/>
     <mergeCell ref="G1:J1"/>
-    <mergeCell ref="A6:A7"/>
     <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
